--- a/MiniTemplate/Datas/mission.xlsx
+++ b/MiniTemplate/Datas/mission.xlsx
@@ -3,13 +3,13 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="30612" yWindow="-8592" windowWidth="30936" windowHeight="16776" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -407,18 +407,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.8"/>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col width="7.109375" customWidth="1" style="2" min="2" max="2"/>
-    <col width="13.44140625" customWidth="1" style="2" min="3" max="3"/>
-    <col width="23.33203125" customWidth="1" style="2" min="4" max="5"/>
-    <col width="25.6640625" customWidth="1" style="2" min="6" max="6"/>
-    <col width="21.44140625" customWidth="1" style="2" min="7" max="7"/>
-    <col width="19.33203125" customWidth="1" style="2" min="8" max="8"/>
-    <col width="25.5546875" customWidth="1" style="2" min="9" max="9"/>
-    <col width="23.33203125" customWidth="1" style="2" min="10" max="10"/>
-    <col width="18.33203125" customWidth="1" style="2" min="11" max="11"/>
+    <col width="7.125" customWidth="1" style="2" min="2" max="2"/>
+    <col width="13.5" customWidth="1" style="2" min="3" max="3"/>
+    <col width="23.375" customWidth="1" style="2" min="4" max="5"/>
+    <col width="25.625" customWidth="1" style="2" min="6" max="6"/>
+    <col width="21.5" customWidth="1" style="2" min="7" max="7"/>
+    <col width="19.375" customWidth="1" style="2" min="8" max="8"/>
+    <col width="25.5" customWidth="1" style="2" min="9" max="9"/>
+    <col width="23.375" customWidth="1" style="2" min="10" max="10"/>
+    <col width="18.375" customWidth="1" style="2" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -504,9 +504,9 @@
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
-        <is>
-          <t>string</t>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
@@ -620,7 +620,7 @@
       </c>
       <c r="F4" s="1" t="inlineStr">
         <is>
-          <t>任务图片路径</t>
+          <t>关联的 item ID</t>
         </is>
       </c>
       <c r="G4" s="1" t="inlineStr">
@@ -668,7 +668,9 @@
           <t>Coin</t>
         </is>
       </c>
-      <c r="F5" s="1" t="n"/>
+      <c r="F5" s="1" t="n">
+        <v>1000</v>
+      </c>
       <c r="G5" s="1" t="n"/>
       <c r="H5" s="0" t="n">
         <v>10000</v>
@@ -745,7 +747,9 @@
           <t>Coin</t>
         </is>
       </c>
-      <c r="F7" s="1" t="inlineStr"/>
+      <c r="F7" s="1" t="n">
+        <v>3000</v>
+      </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
           <t>date:22,2</t>
@@ -791,7 +795,9 @@
           <t>Coin</t>
         </is>
       </c>
-      <c r="F8" s="1" t="inlineStr"/>
+      <c r="F8" s="1" t="n">
+        <v>3000</v>
+      </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
           <t>date:22,2</t>
@@ -837,7 +843,9 @@
           <t>Coin</t>
         </is>
       </c>
-      <c r="F9" s="1" t="inlineStr"/>
+      <c r="F9" s="1" t="n">
+        <v>3000</v>
+      </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
           <t>mission:1001</t>
@@ -883,7 +891,9 @@
           <t>Health</t>
         </is>
       </c>
-      <c r="F10" s="1" t="inlineStr"/>
+      <c r="F10" s="1" t="n">
+        <v>1000</v>
+      </c>
       <c r="G10" s="0" t="inlineStr">
         <is>
           <t>healthBelow:70</t>
@@ -929,7 +939,9 @@
           <t>Health</t>
         </is>
       </c>
-      <c r="F11" s="0" t="inlineStr"/>
+      <c r="F11" s="1" t="n">
+        <v>1000</v>
+      </c>
       <c r="G11" s="0" t="inlineStr">
         <is>
           <t>healthBelow:50</t>
@@ -951,6 +963,446 @@
         </is>
       </c>
       <c r="K11" s="0" t="inlineStr">
+        <is>
+          <t>gameover</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="0" t="n">
+        <v>1010</v>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>翻页测试任务 01</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>用于测试任务列表翻页显示</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G12" s="0" t="inlineStr">
+        <is>
+          <t>date:1,1</t>
+        </is>
+      </c>
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>99,12</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>gameover</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="0" t="n">
+        <v>1011</v>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>翻页测试任务 02</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>用于测试任务列表翻页显示</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G13" s="0" t="inlineStr">
+        <is>
+          <t>date:1,1</t>
+        </is>
+      </c>
+      <c r="H13" s="0" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr">
+        <is>
+          <t>99,12</t>
+        </is>
+      </c>
+      <c r="K13" s="0" t="inlineStr">
+        <is>
+          <t>gameover</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="0" t="n">
+        <v>1012</v>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>翻页测试任务 03</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>用于测试任务列表翻页显示</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G14" s="0" t="inlineStr">
+        <is>
+          <t>date:1,1</t>
+        </is>
+      </c>
+      <c r="H14" s="0" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr">
+        <is>
+          <t>99,12</t>
+        </is>
+      </c>
+      <c r="K14" s="0" t="inlineStr">
+        <is>
+          <t>gameover</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="0" t="n">
+        <v>1013</v>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>翻页测试任务 04</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>用于测试任务列表翻页显示</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G15" s="0" t="inlineStr">
+        <is>
+          <t>date:1,1</t>
+        </is>
+      </c>
+      <c r="H15" s="0" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr">
+        <is>
+          <t>99,12</t>
+        </is>
+      </c>
+      <c r="K15" s="0" t="inlineStr">
+        <is>
+          <t>gameover</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="0" t="n">
+        <v>1014</v>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>翻页测试任务 05</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>用于测试任务列表翻页显示</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G16" s="0" t="inlineStr">
+        <is>
+          <t>date:1,1</t>
+        </is>
+      </c>
+      <c r="H16" s="0" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr">
+        <is>
+          <t>99,12</t>
+        </is>
+      </c>
+      <c r="K16" s="0" t="inlineStr">
+        <is>
+          <t>gameover</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="0" t="n">
+        <v>1015</v>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>翻页测试任务 06</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>用于测试任务列表翻页显示</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>date:1,1</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr">
+        <is>
+          <t>99,12</t>
+        </is>
+      </c>
+      <c r="K17" s="0" t="inlineStr">
+        <is>
+          <t>gameover</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="0" t="n">
+        <v>1016</v>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>翻页测试任务 07</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>用于测试任务列表翻页显示</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G18" s="0" t="inlineStr">
+        <is>
+          <t>date:1,1</t>
+        </is>
+      </c>
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr">
+        <is>
+          <t>99,12</t>
+        </is>
+      </c>
+      <c r="K18" s="0" t="inlineStr">
+        <is>
+          <t>gameover</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="n">
+        <v>1017</v>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>翻页测试任务 08</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>用于测试任务列表翻页显示</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G19" s="0" t="inlineStr">
+        <is>
+          <t>date:1,1</t>
+        </is>
+      </c>
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr">
+        <is>
+          <t>99,12</t>
+        </is>
+      </c>
+      <c r="K19" s="0" t="inlineStr">
+        <is>
+          <t>gameover</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="0" t="n">
+        <v>1018</v>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>翻页测试任务 09</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>用于测试任务列表翻页显示</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G20" s="0" t="inlineStr">
+        <is>
+          <t>date:1,1</t>
+        </is>
+      </c>
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr">
+        <is>
+          <t>99,12</t>
+        </is>
+      </c>
+      <c r="K20" s="0" t="inlineStr">
+        <is>
+          <t>gameover</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="0" t="n">
+        <v>1019</v>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>翻页测试任务 10</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>用于测试任务列表翻页显示</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Coin</t>
+        </is>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G21" s="0" t="inlineStr">
+        <is>
+          <t>date:1,1</t>
+        </is>
+      </c>
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr">
+        <is>
+          <t>99,12</t>
+        </is>
+      </c>
+      <c r="K21" s="0" t="inlineStr">
         <is>
           <t>gameover</t>
         </is>
